--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_BSA.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_BSA.xlsx
@@ -933,7 +933,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>T. Smalls</t>
@@ -2169,7 +2173,11 @@
           <t>BSA_J._WARE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>323112</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>J. Ware</t>
@@ -3017,7 +3025,11 @@
           <t>BSA_J._WARE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>323112</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>J. Ware</t>
@@ -4475,7 +4487,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>T. Smalls</t>
@@ -5353,7 +5369,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>T. Smalls</t>
@@ -6569,7 +6589,11 @@
           <t>BSA_J._WARE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>323112</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>J. Ware</t>
@@ -8153,7 +8177,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>T. Smalls</t>
@@ -9954,7 +9982,11 @@
           <t>BSA_J._WARE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>323112</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>J. Ware</t>
@@ -10048,7 +10080,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>T. Smalls</t>
@@ -10338,7 +10374,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>T. Smalls</t>
@@ -10628,7 +10668,11 @@
           <t>BSA_J._WARE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>323112</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>J. Ware</t>
@@ -11016,7 +11060,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>T. Smalls</t>
@@ -11762,7 +11810,11 @@
           <t>BSA_J._WARE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>323112</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>J. Ware</t>
@@ -12052,7 +12104,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>T. Smalls</t>
@@ -12440,7 +12496,11 @@
           <t>BSA_T._SMALLS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>322770</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>T. Smalls</t>
